--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0088.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0088.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Cluster Effect I</t>
+          <t>Hiệu Ứng Cụm I</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Cluster Effect II</t>
+          <t>Hiệu Ứng Cụm II</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Cluster Effect III</t>
+          <t>Hiệu Ứng Cụm III</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Berserk</t>
+          <t>Cuồng Nộ</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Chrysalis Swarm I</t>
+          <t>Bầy Kén Trưởng Thành I</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Chrysalis Swarm II</t>
+          <t>Bầy Kén Trưởng Thành II</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Healing Prevention I</t>
+          <t>Ngăn hồi phục I</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Healing Prevention I</t>
+          <t>Ngăn hồi phục I</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Teeming Evil</t>
+          <t>Ác Ma Tràn Lan</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Chỉ Áp Dụng Ở Cự Ly Gần</t>
+          <t>Chỉ Trong Tầm Tay</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Ranged Only</t>
+          <t>Tầm Xa</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Amplification I</t>
+          <t>Khuếch Đại I</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Amplification II</t>
+          <t>Khuếch Đại II</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Obstinance I</t>
+          <t>Cố Chấp I</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Obstinance II</t>
+          <t>Cố Chấp II</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Feeble I</t>
+          <t>Kẻ yếu đuối I</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Feeble II</t>
+          <t>Kẻ yếu đuối II</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Delayed Effect I</t>
+          <t>Hiệu ứng trì hoãn I</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Delayed Effect II</t>
+          <t>Hiệu ứng trì hoãn II</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Mô-đun Stress và Hỗ Trợ Đã Mở Khóa</t>
+          <t>Mô-đun Căng Thẳng và Hỗ Trợ Đã Mở Khóa</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Khó</t>
+          <t>Khó khăn</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Extreme</t>
+          <t>Cực Hạn</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Aero Assault</t>
+          <t>Tấn công Aero</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Operation Treatment</t>
+          <t>Điều trị trong nhiệm vụ</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Spectro Assault</t>
+          <t>Tấn công Spectro</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Impenetrable Fortress</t>
+          <t>Pháo Đài Bất Khả Xâm Phạm</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Ethereal Grace</t>
+          <t>Ân Sủng Hư Không</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Lash Healing</t>
+          <t>Liệu Pháp Chữa Lành</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Pre-emptive Strike</t>
+          <t>Tấn công phủ đầu</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Armor Plating</t>
+          <t>Lớp Giáp</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Crisis Response</t>
+          <t>Ứng Phó Khủng Hoảng</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Disaster Response</t>
+          <t>Ứng Phó Thảm Họa</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Daily Crisis Management</t>
+          <t>Xử Lý Khủng Hoảng Hằng Ngày</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Phiên bản thử nghiệm bị khóa</t>
+          <t>Thử thách bị khóa</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Undying Hellfire</t>
+          <t>Hỏa Ngục Bất Diệt</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Bóng Tối Của Cái Chết</t>
+          <t>Bóng Tối Tử Thần</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Mech Rampage</t>
+          <t>Cơn Thịnh Nộ Cơ Khí</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Kỷ lục cao nhất</t>
+          <t>Kỷ Lục Cao Nhất</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Operation Treatment</t>
+          <t>Điều trị trong nhiệm vụ</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Không Quân Tầm Gần</t>
+          <t>Hỗ trợ không kích gần</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Saturation Attack</t>
+          <t>Đòn Bão Hòa</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Growing Outburst</t>
+          <t>Bùng Nổ Sinh Trưởng</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Abnormal Assault</t>
+          <t>Tấn Công Bất Thường</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Impenetrable Fortress</t>
+          <t>Pháo Đài Bất Khả Xâm Phạm</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Armor Plating</t>
+          <t>Lớp Giáp</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Pre-emptive Strike</t>
+          <t>Tấn công phủ đầu</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Trạm tiếp tế</t>
+          <t>Trạm Cung Cấp</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Chi tiết Mô-đun Căng thẳng</t>
+          <t>Chi Tiết Mô-đun Áp Lực</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Hỗ Trợ Details</t>
+          <t>Chi Tiết Hỗ Trợ</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Avinoleum Code I</t>
+          <t>Mã Avinoleum I</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Seminary Code II</t>
+          <t>Mật Mã Chủng Tự II</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>The Fisalia Family Journal I</t>
+          <t>Nhật ký Gia tộc Fisalia I</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>The Fisalia Family Journal II</t>
+          <t>Nhật ký Gia tộc Fisalia II</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Phụ "Scale of Past" và Nhiệm Vụ Sự Kiện "Cube, Cubic n Cubie" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Phụ "Cán Cân Quá Khứ" và Nhiệm Vụ Sự Kiện "Cube, Cubic n Cubie" để mở khóa</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Điểm chiến đấu</t>
+          <t>Điểm Chiến Đấu</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Điểm vòng</t>
+          <t>Điểm Vòng</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>June 18</t>
+          <t>Ngày 18 tháng 6</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>The Fisalia Family</t>
+          <t>Gia tộc Fisalia</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Biển Của Những Giấc Mơ</t>
+          <t>Biển Mộng Ảo</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Tiểu Mễ</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Coral Parasol</t>
+          <t>Ô San Hô</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Nồi Mộng Đẹp</t>
+          <t>Nồi Mộng Mơ Ngọt Ngào</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Potion Vial</t>
+          <t>Lọ Thuốc</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Round Table</t>
+          <t>Bàn Vòng</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Jellyfish Lamp</t>
+          <t>Đèn Sứa</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Uncaged Bird</t>
+          <t>Chim Lồng Vỡ Tổ</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Lucid Dream</t>
+          <t>Giấc Mơ Sáng Suốt</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Assist</t>
+          <t>Hỗ trợ</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Bừng Sáng Bình Minh</t>
+          <t>Bình Minh Ló Rạng</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Complete Boat Racing I</t>
+          <t>Hoàn thành Đua Thuyền I</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Complete Ace Wings II</t>
+          <t>Hoàn thành Ace Wings II</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách trong khu vực ẩn tại "Nếu Sao Băng Rực Cháy"</t>
+          <t>Hoàn thành thử thách trong khu vực ẩn của "Nếu Sao Băng Rực Cháy"</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Đánh Bại Coercitors: Phán Quyết</t>
+          <t>Hạ gục Coercitors: The Verdict</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Đã áp dụng cài đặt màu sắc</t>
+          <t>Cài đặt màu sắc đã được áp dụng</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Ace Wings</t>
+          <t>Đôi Cánh Phi Thường</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Boat Racing</t>
+          <t>Đua Thuyền</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Flash Dodge</t>
+          <t>Né Tia Chớp</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Thiếu Nữ, Kẻ Nổi Loạn, Kẻ Rao Tin Tử Thần" để mở khóa</t>
+          <t>Hoàn thành Nhiệm Vụ Chính "Thiếu Nữ, Kẻ Nổi Loạn, Người Rao Tử Thần" để mở khóa</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Bạn không còn Cơ Hội Hồi Sinh</t>
+          <t>Ngươi không còn Cơ Hội Hồi Sinh nào nữa.</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Test I</t>
+          <t>Kiểm Tra I</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Test II</t>
+          <t>Kiểm Tra II</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Test III</t>
+          <t>Kiểm Tra III</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Test IV</t>
+          <t>Kiểm Tra IV</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Glider</t>
+          <t>Dù lượn</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Flight</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Path</t>
+          <t>Con đường</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Thử nghiệm/Chiếm giữ</t>
+          <t>Chiếm giữ</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21854,7 +21854,8 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>[Vui lòng nhập tiêu đề phụ cho cấp độ của bạn tại đây]</t>
+          <t>[
+Vui lòng nhập tiêu đề phụ cho cấp độ của bạn tại đây]</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21925,8 +21926,8 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Hợp tác)
-Lượt hồi sinh chung: 6</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+Cơ hội hồi sinh chung: 6</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21997,8 +21998,8 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Thời gian hồi sinh: 10 giây (Chơi đơn &amp; Hợp tác)
-Lượt hồi sinh chung: 9</t>
+          <t>Thời gian hồi sinh: 10 giây (Solo &amp; Co-op)
+Cơ hội hồi sinh chung: 9</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22138,7 +22139,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Trinity Force</t>
+          <t>Lực Ba Nguyên</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22208,7 +22209,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>A Quiet Underworld</t>
+          <t>Thế Giới Ngầm Tĩnh Lặng</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22278,7 +22279,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Thế Giới Sẽ Đạt Tới Hoàng Hôn</t>
+          <t>Thế Giới Sẽ Đi Tới Hoàng Hôn</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22348,7 +22349,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>I See Fire</t>
+          <t>Ta Thấy Lửa</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22418,7 +22419,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Wind Talker</t>
+          <t>Người Nói Chuyện Với Gió</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22488,7 +22489,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Aspect</t>
+          <t>Phiên Bản Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22558,7 +22559,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Đôi Cánh Của Sứ Giả</t>
+          <t>Đôi Cánh Sứ Giả</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22628,7 +22629,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Tiêu Chuẩn Aspect</t>
+          <t>Phiên Bản Tiêu Chuẩn</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22698,7 +22699,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22768,7 +22769,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Warrior's Deeds</t>
+          <t>Chiến Công của Chiến Binh</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22838,7 +22839,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Warrior's Challenges</t>
+          <t>Những Thử Thách của Chiến Binh</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22908,7 +22909,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Activated</t>
+          <t>Đã kích hoạt</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23048,7 +23049,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Bạn Đồng Hành Mới</t>
+          <t>Đồng Hành Mới</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23118,7 +23119,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23188,7 +23189,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Mô-đun Slot</t>
+          <t>Khe Mô-đun</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23258,7 +23259,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Không thể trang bị Mô-đun của chính Resonator</t>
+          <t>Không thể trang bị Module của chính Resonator này</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23328,7 +23329,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Không thể trang bị hai hoặc nhiều Passive Mô-đun giống nhau</t>
+          <t>Không thể trang bị hai hay nhiều Module Bị Động giống nhau</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23398,7 +23399,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Download Complete</t>
+          <t>Tải Hoàn Tất</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23468,7 +23469,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Pre-download</t>
+          <t>Tải trước</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23538,7 +23539,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Tidal Festivities</t>
+          <t>Lễ hội Thủy Triều</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23608,7 +23609,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Resounding Waves</t>
+          <t>Sóng Âm Vang Xa</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23678,7 +23679,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Summertime Trang phục</t>
+          <t>Trang Phục Mùa Hè</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23748,7 +23749,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Chúng Ta Nhẹ Nhàng Ném Vòng Ngọc</t>
+          <t>Chúng ta nhẹ nhàng ném vương miện</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23818,7 +23819,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23888,7 +23889,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24098,7 +24099,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Woven Melodies</t>
+          <t>Giai Điệu Dệt Nên</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24168,7 +24169,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Ye Zhiqiu</t>
+          <t>Diệp Chi Thu</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24448,7 +24449,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24518,7 +24519,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24658,7 +24659,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>The Montelli Family</t>
+          <t>Gia Tộc Montelli</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -25078,7 +25079,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Ngòi Bút Thơ Ca</t>
+          <t>Ngòi Bút Thi Ca</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25148,7 +25149,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Miniature Instrument</t>
+          <t>Nhạc cụ thu nhỏ</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25218,7 +25219,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Musical Remembrance</t>
+          <t>Ký Ức Âm Nhạc</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25288,7 +25289,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Personal Memo</t>
+          <t>Ghi Chú Cá Nhân</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25428,7 +25429,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Món Quà Biết Ơn</t>
+          <t>Món Quà Tri Ân</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25568,7 +25569,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Thơ Ca và Thế Giới</t>
+          <t>Thi Ca và Thế Gian</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25638,7 +25639,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Số Mệnh và Cánh Cửa</t>
+          <t>Định Mệnh và Cánh Cửa</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25708,7 +25709,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Vì Những Câu Chuyện, Nàng Sẽ Hát</t>
+          <t>Vì Những Câu Chuyện, Nàng Sẽ Hát Ca</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25778,7 +25779,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>For Herself, Cô ấy Shall Sing</t>
+          <t>Vì Chính Nàng, Nàng Sẽ Hát</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25848,7 +25849,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>"A Regular"</t>
+          <t>"Một Người Bình Thường"</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25918,7 +25919,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Bóng Tối Của Ngọn Lửa</t>
+          <t>Bóng Tối Lửa Đỏ</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25988,7 +25989,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Best Employee</t>
+          <t>Nhân Viên Xuất Sắc Nhất</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26058,7 +26059,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Night's Solitary Path</t>
+          <t>Con Đường Cô Đơn Của Đêm</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26128,7 +26129,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Đêm Trước Lễ Hội Carnevale</t>
+          <t>Đêm trước Lễ Hội Carnevale</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -35298,7 +35299,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Tải tài nguyên câu chuyện để tiếp tục</t>
+          <t>Tải xuống dữ liệu câu chuyện để tiếp tục</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35368,7 +35369,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Sự Thật Về Daemon</t>
+          <t>Chân Lý Của Ma Quỷ</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35438,7 +35439,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Những Bản Nhạc Ngày Xưa</t>
+          <t>Khúc Ca Ngày Xưa</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35508,7 +35509,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Sân Khấu Đã Sẵn Sàng</t>
+          <t>Màn Đã Dựng Xong</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
